--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.76182225804444</v>
+        <v>7.111296116932222</v>
       </c>
       <c r="D2" t="n">
-        <v>43.17487123595971</v>
+        <v>7.015916575843454</v>
       </c>
       <c r="E2" t="n">
-        <v>19.43850508593351</v>
+        <v>3.158757076464195</v>
       </c>
       <c r="F2" t="n">
-        <v>19.48263661726565</v>
+        <v>3.165928450305668</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.54072269715829</v>
+        <v>2.850367438288222</v>
       </c>
       <c r="D3" t="n">
-        <v>16.61448454564493</v>
+        <v>2.699853738667302</v>
       </c>
       <c r="E3" t="n">
-        <v>19.43850508593351</v>
+        <v>3.158757076464195</v>
       </c>
       <c r="F3" t="n">
-        <v>19.48263661726565</v>
+        <v>3.165928450305668</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.7261630061839</v>
+        <v>7.593001488504883</v>
       </c>
       <c r="D4" t="n">
-        <v>46.78269655077729</v>
+        <v>7.60218818950131</v>
       </c>
       <c r="E4" t="n">
-        <v>19.43850508593351</v>
+        <v>3.158757076464195</v>
       </c>
       <c r="F4" t="n">
-        <v>19.48263661726565</v>
+        <v>3.165928450305668</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>72.43997454238684</v>
+        <v>11.77149586313786</v>
       </c>
       <c r="D5" t="n">
-        <v>71.58745534333266</v>
+        <v>11.63296149329156</v>
       </c>
       <c r="E5" t="n">
-        <v>19.43850508593351</v>
+        <v>3.158757076464195</v>
       </c>
       <c r="F5" t="n">
-        <v>19.48263661726565</v>
+        <v>3.165928450305668</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
